--- a/results/tables/Summary_of_analysises_torress_ITT.xlsx
+++ b/results/tables/Summary_of_analysises_torress_ITT.xlsx
@@ -1625,13 +1625,13 @@
     <t xml:space="preserve">0.63 (0.1 - 4.01)</t>
   </si>
   <si>
-    <t xml:space="preserve">0 (0 - 123425.5)</t>
+    <t xml:space="preserve">0 (0 - 123419.95)</t>
   </si>
   <si>
     <t xml:space="preserve">0.97 (0.13 - 7.24)</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01 (0.01 - 10463.37)</t>
+    <t xml:space="preserve">9.01 (0.01 - 10463.27)</t>
   </si>
   <si>
     <t xml:space="preserve">0.05 (0.01 - 0.43)</t>
@@ -4581,7 +4581,7 @@
         <v>495</v>
       </c>
       <c r="C15" t="n">
-        <v>0.932</v>
+        <v>0.931</v>
       </c>
       <c r="D15" t="s">
         <v>496</v>
@@ -5547,13 +5547,13 @@
         <v>528</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0229414287452236</v>
+        <v>0.0229412483464859</v>
       </c>
       <c r="D2" t="s">
         <v>529</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0183946597309759</v>
+        <v>0.0183944496288493</v>
       </c>
     </row>
     <row r="3">
@@ -5564,13 +5564,13 @@
         <v>530</v>
       </c>
       <c r="C3" t="n">
-        <v>0.951568231480448</v>
+        <v>0.951568220990294</v>
       </c>
       <c r="D3" t="s">
         <v>531</v>
       </c>
       <c r="E3" t="n">
-        <v>0.872723965654278</v>
+        <v>0.872723929641282</v>
       </c>
     </row>
     <row r="4">
@@ -5581,13 +5581,13 @@
         <v>532</v>
       </c>
       <c r="C4" t="n">
-        <v>0.691642954175478</v>
+        <v>0.691642881004529</v>
       </c>
       <c r="D4" t="s">
         <v>533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.831956378831858</v>
+        <v>0.831956330695365</v>
       </c>
     </row>
     <row r="5">
@@ -5598,13 +5598,13 @@
         <v>534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.624227646338268</v>
+        <v>0.624227553422698</v>
       </c>
       <c r="D5" t="s">
         <v>535</v>
       </c>
       <c r="E5" t="n">
-        <v>0.203536340822412</v>
+        <v>0.203536012173079</v>
       </c>
     </row>
     <row r="6">
@@ -5615,13 +5615,13 @@
         <v>536</v>
       </c>
       <c r="C6" t="n">
-        <v>0.973010054203512</v>
+        <v>0.973010048367498</v>
       </c>
       <c r="D6" t="s">
         <v>537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.537662368487108</v>
+        <v>0.53766221224931</v>
       </c>
     </row>
     <row r="7">
@@ -5632,13 +5632,13 @@
         <v>538</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00637833719546759</v>
+        <v>0.00637824257587229</v>
       </c>
       <c r="D7" t="s">
         <v>539</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00519613472781332</v>
+        <v>0.00519602706951407</v>
       </c>
     </row>
     <row r="8">
@@ -5649,13 +5649,13 @@
         <v>540</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0282549320092889</v>
+        <v>0.028254735619851</v>
       </c>
       <c r="D8" t="s">
         <v>541</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0207010225017937</v>
+        <v>0.0207008009593939</v>
       </c>
     </row>
     <row r="9">
@@ -5666,13 +5666,13 @@
         <v>542</v>
       </c>
       <c r="C9" t="n">
-        <v>0.125499406016137</v>
+        <v>0.125499133361451</v>
       </c>
       <c r="D9" t="s">
         <v>543</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0859926800857872</v>
+        <v>0.0859923373301872</v>
       </c>
     </row>
     <row r="10">
@@ -5683,13 +5683,13 @@
         <v>544</v>
       </c>
       <c r="C10" t="n">
-        <v>0.196175133194298</v>
+        <v>0.1961748753956</v>
       </c>
       <c r="D10" t="s">
         <v>545</v>
       </c>
       <c r="E10" t="n">
-        <v>0.105963252682223</v>
+        <v>0.105962903158237</v>
       </c>
     </row>
     <row r="11">
@@ -5700,7 +5700,7 @@
         <v>546</v>
       </c>
       <c r="C11" t="n">
-        <v>0.993706516049862</v>
+        <v>0.993706514690013</v>
       </c>
       <c r="D11" t="s">
         <v>547</v>
@@ -5717,13 +5717,13 @@
         <v>548</v>
       </c>
       <c r="C12" t="n">
-        <v>0.37480119543607</v>
+        <v>0.374801010906892</v>
       </c>
       <c r="D12" t="s">
         <v>549</v>
       </c>
       <c r="E12" t="n">
-        <v>0.257201550927382</v>
+        <v>0.257201248792603</v>
       </c>
     </row>
   </sheetData>
@@ -5774,13 +5774,13 @@
         <v>557</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0416719368301677</v>
+        <v>0.0416707477027412</v>
       </c>
       <c r="E2" t="s">
         <v>558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0721430852448864</v>
+        <v>0.0721382914698594</v>
       </c>
       <c r="G2" t="n">
         <v>0.072</v>
@@ -5800,13 +5800,13 @@
         <v>561</v>
       </c>
       <c r="D3" t="n">
-        <v>0.965666946398298</v>
+        <v>0.965666938906637</v>
       </c>
       <c r="E3" t="s">
         <v>562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.981719353361427</v>
+        <v>0.981719348216669</v>
       </c>
       <c r="G3" t="n">
         <v>0.718</v>
@@ -5826,13 +5826,13 @@
         <v>564</v>
       </c>
       <c r="D4" t="n">
-        <v>0.557260726758487</v>
+        <v>0.557260300680316</v>
       </c>
       <c r="E4" t="s">
         <v>565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.940658743115446</v>
+        <v>0.940658651799388</v>
       </c>
       <c r="G4" t="n">
         <v>0.258</v>
@@ -5852,13 +5852,13 @@
         <v>567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.95460565614367</v>
+        <v>0.954605644150473</v>
       </c>
       <c r="E5" t="s">
         <v>568</v>
       </c>
       <c r="F5" t="n">
-        <v>0.643124361112465</v>
+        <v>0.643124224646014</v>
       </c>
       <c r="G5" t="n">
         <v>0.181</v>
